--- a/Categoría/RUC_Categoría.xlsx
+++ b/Categoría/RUC_Categoría.xlsx
@@ -833,13 +833,13 @@
         <v>1.45877759618311</v>
       </c>
       <c r="C2" s="2">
-        <v>112.2262160580291</v>
+        <v>111.7005326165214</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.63713089689858</v>
+        <v>1.629462344627021</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="2">
-        <v>2.747358120436118</v>
+        <v>2.747358120436116</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1969,7 +1969,7 @@
         <v>73</v>
       </c>
       <c r="B69" s="2">
-        <v>1.397801965188806</v>
+        <v>1.397801965188807</v>
       </c>
       <c r="C69" s="2">
         <v>112.9661257265843</v>
@@ -1978,7 +1978,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>1.579042725403854</v>
+        <v>1.579042725403853</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2003,10 +2003,10 @@
         <v>75</v>
       </c>
       <c r="B71" s="2">
-        <v>0.5973104237677945</v>
+        <v>0.5973104237677944</v>
       </c>
       <c r="C71" s="2">
-        <v>115.1438838516155</v>
+        <v>115.1438838516156</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>6</v>
@@ -2890,13 +2890,13 @@
         <v>3.740094893016188</v>
       </c>
       <c r="C123" s="2">
-        <v>136.0340850535815</v>
+        <v>136.0340850535816</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E123" s="2">
-        <v>5.0878038678503</v>
+        <v>5.087803867850302</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2921,7 +2921,7 @@
         <v>129</v>
       </c>
       <c r="B125" s="2">
-        <v>7.065896683818083</v>
+        <v>7.065896683818084</v>
       </c>
       <c r="C125" s="2">
         <v>111.6370980743197</v>
@@ -3151,7 +3151,7 @@
         <v>6</v>
       </c>
       <c r="E138" s="2">
-        <v>0.831882867361269</v>
+        <v>0.8318828673612693</v>
       </c>
     </row>
     <row r="139" spans="1:5">
